--- a/Documentation/classes_inscription/class_MovingTile.xlsx
+++ b/Documentation/classes_inscription/class_MovingTile.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Main_for_all\Python_Projects\MathUp\Documentation\classes_inscription\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\classes_inscription\classes_inscription\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09E03AA0-1432-43E5-B2E9-C7903385B74C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E5F9D9CB-3CD7-4917-8567-0B1D80747591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="גיליון1" sheetId="1" r:id="rId1"/>
@@ -51,13 +51,13 @@
     <t>y_change</t>
   </si>
   <si>
-    <t>מתארת את שינוי של מיקום בציר y של עצם ב-tick.</t>
-  </si>
-  <si>
     <t>update</t>
   </si>
   <si>
-    <t>מעדכן את המיקום של אובייקט בהתאם לתכונה - y_change</t>
+    <t>מתארת את השינוי של המיקום בציר y של עצם ב-tick.</t>
+  </si>
+  <si>
+    <t>מעדכנת את המיקום של האובייקט בהתאם לתכונה - y_change</t>
   </si>
 </sst>
 </file>
@@ -189,11 +189,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -205,14 +212,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -494,7 +493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="30.7109375" customWidth="1"/>
@@ -503,22 +502,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="5"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="8"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="6" t="s">
+      <c r="B2" s="10"/>
+      <c r="C2" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="7"/>
+      <c r="D2" s="10"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -538,111 +537,15 @@
       <c r="A4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="6" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="3">
